--- a/overall_model_dataset_log.xlsx
+++ b/overall_model_dataset_log.xlsx
@@ -1,46 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Model IP Protection\locking model scheme\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C62EC0-557D-4382-9515-12814B61D24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
+  <si>
+    <t>resnet18</t>
+  </si>
+  <si>
+    <t>vgg16</t>
+  </si>
+  <si>
+    <t>wideresnet-50</t>
+  </si>
+  <si>
+    <t>GoogLeNet</t>
+  </si>
+  <si>
+    <t>dataset</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>homogeneous</t>
+  </si>
+  <si>
+    <t>locked</t>
+  </si>
+  <si>
+    <t>assembled</t>
+  </si>
+  <si>
+    <t>MNIST</t>
+  </si>
+  <si>
+    <t>99.76</t>
+  </si>
+  <si>
+    <t>99.74</t>
+  </si>
+  <si>
+    <t>9.74</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>cifar-10</t>
+  </si>
+  <si>
+    <t>95.09</t>
+  </si>
+  <si>
+    <t>95.01</t>
+  </si>
+  <si>
+    <t>7.06</t>
+  </si>
+  <si>
+    <t>91.78</t>
+  </si>
+  <si>
+    <t>91.80</t>
+  </si>
+  <si>
+    <t>cifar-100</t>
+  </si>
+  <si>
+    <t>77.77</t>
+  </si>
+  <si>
+    <t>75.97</t>
+  </si>
+  <si>
+    <t>1.19</t>
+  </si>
+  <si>
+    <t>ImageNet</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -64,14 +137,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,180 +483,251 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="str">
-        <v>resnet18</v>
-      </c>
-      <c r="F1" t="str">
-        <v>vgg16</v>
-      </c>
-      <c r="J1" t="str">
-        <v>wideresnet-50</v>
-      </c>
-      <c r="N1" t="str">
-        <v>GoogLeNet</v>
-      </c>
+    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>dataset</v>
-      </c>
-      <c r="B2" t="str">
-        <v>base</v>
-      </c>
-      <c r="C2" t="str">
-        <v>homogeneous</v>
-      </c>
-      <c r="D2" t="str">
-        <v>locked</v>
-      </c>
-      <c r="E2" t="str">
-        <v>assembled</v>
-      </c>
-      <c r="F2" t="str">
-        <v>base</v>
-      </c>
-      <c r="G2" t="str">
-        <v>homogeneous</v>
-      </c>
-      <c r="H2" t="str">
-        <v>locked</v>
-      </c>
-      <c r="I2" t="str">
-        <v>assembled</v>
-      </c>
-      <c r="J2" t="str">
-        <v>base</v>
-      </c>
-      <c r="K2" t="str">
-        <v>homogeneous</v>
-      </c>
-      <c r="L2" t="str">
-        <v>locked</v>
-      </c>
-      <c r="M2" t="str">
-        <v>assembled</v>
-      </c>
-      <c r="N2" t="str">
-        <v>base</v>
-      </c>
-      <c r="O2" t="str">
-        <v>homogeneous</v>
-      </c>
-      <c r="P2" t="str">
-        <v>locked</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>assembled</v>
+    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>MNIST</v>
-      </c>
-      <c r="B3" t="str">
-        <v>99.76</v>
-      </c>
-      <c r="C3" t="str">
-        <v>99.74</v>
-      </c>
-      <c r="D3" t="str">
-        <v>9.74</v>
-      </c>
-      <c r="E3" t="str">
-        <v>99.74</v>
-      </c>
-      <c r="I3" t="str">
-        <v>0</v>
-      </c>
-      <c r="M3" t="str">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>0</v>
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2">
+        <v>99.53</v>
+      </c>
+      <c r="G3" s="2">
+        <v>99.58</v>
+      </c>
+      <c r="H3" s="2">
+        <v>10.09</v>
+      </c>
+      <c r="I3" s="2">
+        <v>99.58</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>cifar-10</v>
-      </c>
-      <c r="B4" t="str">
-        <v>95.09</v>
-      </c>
-      <c r="C4" t="str">
-        <v>95.01</v>
-      </c>
-      <c r="D4" t="str">
-        <v>7.06</v>
-      </c>
-      <c r="E4" t="str">
-        <v>95.01</v>
-      </c>
-      <c r="F4" t="str">
-        <v>91.78</v>
-      </c>
-      <c r="G4" t="str">
-        <v>91.80</v>
-      </c>
-      <c r="I4" t="str">
-        <v>91.80</v>
-      </c>
-      <c r="M4" t="str">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>0</v>
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>cifar-100</v>
-      </c>
-      <c r="B5" t="str">
-        <v>77.77</v>
-      </c>
-      <c r="C5" t="str">
-        <v>75.97</v>
-      </c>
-      <c r="D5" t="str">
-        <v>1.19</v>
-      </c>
-      <c r="E5" t="str">
-        <v>75.97</v>
-      </c>
-      <c r="I5" t="str">
-        <v>0</v>
-      </c>
-      <c r="M5" t="str">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>0</v>
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2">
+        <v>69.31</v>
+      </c>
+      <c r="G5" s="2">
+        <v>68.81</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1.21</v>
+      </c>
+      <c r="I5" s="2">
+        <v>68.81</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ImageNet</v>
-      </c>
-      <c r="E6" t="str">
-        <v>0</v>
-      </c>
-      <c r="I6" t="str">
-        <v>0</v>
-      </c>
-      <c r="M6" t="str">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>0</v>
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q6"/>
+    <ignoredError sqref="A2:Q2 A1:B1 F1 J1:Q1 A6:Q6 A5:E5 J5:Q5 A4:G4 I4:Q4 A3:E3 J3:Q3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/overall_model_dataset_log.xlsx
+++ b/overall_model_dataset_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Model IP Protection\locking model scheme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C62EC0-557D-4382-9515-12814B61D24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3AD929-7BF4-4B95-8D93-08DE6D6987AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>resnet18</t>
   </si>
@@ -61,6 +61,15 @@
     <t>9.74</t>
   </si>
   <si>
+    <t>99.53</t>
+  </si>
+  <si>
+    <t>99.58</t>
+  </si>
+  <si>
+    <t>10.09</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
@@ -82,6 +91,18 @@
     <t>91.80</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>91.84</t>
+  </si>
+  <si>
+    <t>91.75</t>
+  </si>
+  <si>
+    <t>10.08</t>
+  </si>
+  <si>
     <t>cifar-100</t>
   </si>
   <si>
@@ -94,7 +115,28 @@
     <t>1.19</t>
   </si>
   <si>
+    <t>69.31</t>
+  </si>
+  <si>
+    <t>68.81</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>78.67</t>
+  </si>
+  <si>
+    <t>78.72</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
     <t>ImageNet</t>
+  </si>
+  <si>
+    <t>89.10</t>
   </si>
 </sst>
 </file>
@@ -485,22 +527,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.796875" style="1"/>
+    <col min="2" max="17" width="11.5" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.796875" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
       <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
@@ -514,220 +560,255 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2">
-        <v>99.53</v>
-      </c>
-      <c r="G3" s="2">
-        <v>99.58</v>
-      </c>
-      <c r="H3" s="2">
-        <v>10.09</v>
-      </c>
-      <c r="I3" s="2">
-        <v>99.58</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2" t="s">
-        <v>13</v>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1">
+        <v>99.67</v>
+      </c>
+      <c r="K3" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="L3" s="1">
+        <v>9.89</v>
+      </c>
+      <c r="M3" s="1">
+        <v>99.7</v>
+      </c>
+      <c r="N3" s="1">
+        <v>99.73</v>
+      </c>
+      <c r="O3" s="1">
+        <v>99.74</v>
+      </c>
+      <c r="P3" s="1">
+        <v>10.14</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>99.74</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    <row r="4" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="N4" s="1">
+        <v>94.57</v>
+      </c>
+      <c r="O4" s="1">
+        <v>94.17</v>
+      </c>
+      <c r="P4" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>94.17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2">
-        <v>10</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2" t="s">
-        <v>13</v>
+      <c r="N5" s="1">
+        <v>74.930000000000007</v>
+      </c>
+      <c r="O5" s="1">
+        <v>75.09</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>75.09</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="2">
-        <v>69.31</v>
-      </c>
-      <c r="G5" s="2">
-        <v>68.81</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1.21</v>
-      </c>
-      <c r="I5" s="2">
-        <v>68.81</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2" t="s">
-        <v>13</v>
+    <row r="6" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1">
+        <v>88.73</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="E6" s="1">
+        <v>88.73</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:Q1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:Q2 A1:B1 F1 J1:Q1 A6:Q6 A5:E5 J5:Q5 A4:G4 I4:Q4 A3:E3 J3:Q3" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:Q2 A1:B1 F1 J1 N1 A6:B6 A3:I3 A4:M4 A5:M5 F6:Q6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/overall_model_dataset_log.xlsx
+++ b/overall_model_dataset_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Model IP Protection\locking model scheme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3AD929-7BF4-4B95-8D93-08DE6D6987AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FE5C2E-6C26-485D-BB88-D8EC5C7FE234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
   <si>
     <t>resnet18</t>
   </si>
@@ -70,9 +70,6 @@
     <t>10.09</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>cifar-10</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
   </si>
   <si>
     <t>78.67</t>
-  </si>
-  <si>
-    <t>78.72</t>
   </si>
   <si>
     <t>1.15</t>
@@ -179,8 +173,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -535,30 +532,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
     </row>
     <row r="2" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -668,43 +665,43 @@
     </row>
     <row r="4" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>16</v>
+      <c r="M4" s="2">
+        <v>91.75</v>
       </c>
       <c r="N4" s="1">
         <v>94.57</v>
@@ -721,43 +718,43 @@
     </row>
     <row r="5" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1">
+        <v>78.72</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>16</v>
+      <c r="M5" s="2">
+        <v>78.72</v>
       </c>
       <c r="N5" s="1">
         <v>74.930000000000007</v>
@@ -774,28 +771,55 @@
     </row>
     <row r="6" spans="1:17" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1">
         <v>88.73</v>
       </c>
       <c r="D6" s="1">
-        <v>0.48</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="E6" s="1">
         <v>88.73</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>16</v>
+      <c r="F6" s="1">
+        <v>90.12</v>
+      </c>
+      <c r="G6" s="1">
+        <v>89.98</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="I6" s="1">
+        <v>89.98</v>
+      </c>
+      <c r="J6" s="1">
+        <v>93.84</v>
+      </c>
+      <c r="K6" s="1">
+        <v>93.61</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="M6" s="1">
+        <v>93.61</v>
+      </c>
+      <c r="N6" s="1">
+        <v>89.86</v>
+      </c>
+      <c r="O6" s="1">
+        <v>89.45</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>89.45</v>
       </c>
     </row>
   </sheetData>
@@ -808,7 +832,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:Q2 A1:B1 F1 J1 N1 A6:B6 A3:I3 A4:M4 A5:M5 F6:Q6" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:Q2 A1:B1 F1 J1 N1 A6:B6 A3:I3 A4:L4 A5:J5 L5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>